--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_243_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_243_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.052</v>
+        <v>1.4361</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6733</v>
+        <v>0.1582</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3787</v>
+        <v>1.2778</v>
       </c>
       <c r="G2" t="n">
         <v>2.5492</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0337</v>
+        <v>0.4178</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6097</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4239</v>
+        <v>0.3231</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3303</v>
+        <v>-0.4168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3037</v>
+        <v>-1.7695</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.634</v>
+        <v>1.3527</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3021</v>
+        <v>-0.5987</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4059</v>
+        <v>-0.5317</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1038</v>
+        <v>-0.067</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1947</v>
+        <v>-0.0046</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1947</v>
+        <v>1.2134</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.2181</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1074</v>
+        <v>-0.5941</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2112</v>
+        <v>-1.7452</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1038</v>
+        <v>1.1511</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4383</v>
+        <v>0.1819</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5885</v>
+        <v>0.0907</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1502</v>
+        <v>0.0912</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1811</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0408</v>
+        <v>-0.7302</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1403</v>
+        <v>-0.2411</v>
       </c>
       <c r="G4" t="n">
         <v>-2.4154</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0672</v>
+        <v>0.1426</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2082</v>
+        <v>0.1024</v>
       </c>
       <c r="U4" t="n">
-        <v>0.141</v>
+        <v>0.0402</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2493</v>
+        <v>-1.1395</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.434</v>
+        <v>-0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1847</v>
+        <v>-0.4996</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5987</v>
+        <v>-0.3021</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5317</v>
+        <v>-0.4059</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.067</v>
+        <v>0.1038</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0046</v>
+        <v>-0.1947</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2134</v>
+        <v>-0.1947</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2181</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5941</v>
+        <v>-0.1074</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7452</v>
+        <v>-0.2112</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1511</v>
+        <v>0.1038</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6506</v>
+        <v>0.6291</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5737</v>
+        <v>0.6449</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0769</v>
+        <v>-0.0158</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7736</v>
+        <v>-1.5339</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.396</v>
+        <v>-1.1451</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3776</v>
+        <v>-0.3888</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9391</v>
+        <v>-0.8612</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3697</v>
+        <v>-1.6206</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3088</v>
+        <v>0.7593</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.423</v>
+        <v>1.3088</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9361</v>
+        <v>0.1246</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.359</v>
+        <v>1.1842</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5161</v>
+        <v>-2.17</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5664</v>
+        <v>-1.7452</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0502</v>
+        <v>-0.4248</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8556</v>
+        <v>-3.7112</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7196</v>
+        <v>0.4149</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6686</v>
+        <v>0.1852</v>
       </c>
       <c r="U6" t="n">
-        <v>0.051</v>
+        <v>0.2298</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1352</v>
+        <v>-1.8168</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.5509</v>
+        <v>-0.4393</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4157</v>
+        <v>-1.3776</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.6704</v>
+        <v>-1.9391</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3588</v>
+        <v>0.3697</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3117</v>
+        <v>-2.3088</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.6943</v>
+        <v>-0.423</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.3892</v>
+        <v>1.9361</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3051</v>
+        <v>-2.359</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9761</v>
+        <v>-1.5161</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9696</v>
+        <v>-1.5664</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0065</v>
+        <v>0.0502</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6796</v>
+        <v>0.6763</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3927</v>
+        <v>0.6253</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0723</v>
+        <v>0.051</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5014</v>
+        <v>-2.4228</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0454</v>
+        <v>-4.4016</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.456</v>
+        <v>1.9788</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8612</v>
+        <v>-4.6704</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6206</v>
+        <v>-3.3588</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7593</v>
+        <v>-1.3117</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3088</v>
+        <v>-3.6943</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1246</v>
+        <v>-2.3892</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1842</v>
+        <v>-1.3051</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.17</v>
+        <v>-0.9761</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7452</v>
+        <v>-0.9696</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4248</v>
+        <v>-0.0065</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7112</v>
+        <v>-0.4639</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5526</v>
+        <v>0.3921</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.2434</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1625</v>
+        <v>0.6355</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5598</v>
+        <v>-3.1578</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6114</v>
+        <v>-2.2873</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0516</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8529</v>
+        <v>-4.0591</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5676</v>
+        <v>-1.4392</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2853</v>
+        <v>-2.6199</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8269</v>
+        <v>-2.1646</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6519</v>
+        <v>-0.7023</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.175</v>
+        <v>-1.4623</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.026</v>
+        <v>-1.8945</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9157</v>
+        <v>-0.7369</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1103</v>
+        <v>-1.1577</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8988</v>
+        <v>-0.1709</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5351</v>
+        <v>-0.0351</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3637</v>
+        <v>-0.1357</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8313</v>
+        <v>-3.839</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7591</v>
+        <v>-3.5062</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0722</v>
+        <v>-0.3328</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0591</v>
+        <v>-3.581</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4392</v>
+        <v>-1.5533</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6199</v>
+        <v>-2.0277</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1646</v>
+        <v>-1.5894</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7023</v>
+        <v>0.696</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4623</v>
+        <v>-2.2854</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8945</v>
+        <v>-1.9916</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7369</v>
+        <v>-2.2493</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1577</v>
+        <v>0.2578</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-3.0154</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8443000000000001</v>
+        <v>0.5977</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.507</v>
+        <v>0.5625</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3374</v>
+        <v>0.0351</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2407</v>
+        <v>-4.1421</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7735</v>
+        <v>-5.1264</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4672</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.581</v>
+        <v>-3.8529</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5533</v>
+        <v>-1.5676</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0277</v>
+        <v>-2.2853</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5894</v>
+        <v>-2.8269</v>
       </c>
       <c r="K11" t="n">
-        <v>0.696</v>
+        <v>-0.6519</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2854</v>
+        <v>-2.175</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9916</v>
+        <v>-1.026</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2493</v>
+        <v>-0.9157</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2578</v>
+        <v>-0.1103</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0154</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1959</v>
+        <v>0.3165</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2952</v>
+        <v>0.02</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0993</v>
+        <v>0.2965</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7507</v>
+        <v>-18.0039</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.6341</v>
+        <v>-19.8874</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8834</v>
+        <v>1.8833</v>
       </c>
       <c r="G12" t="n">
         <v>-19.7307</v>
@@ -1366,7 +1366,7 @@
         <v>-7.020200000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>3.436999999999999</v>
+        <v>3.437</v>
       </c>
       <c r="L12" t="n">
         <v>-10.4573</v>
@@ -1378,7 +1378,7 @@
         <v>-12.4104</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3002000000000001</v>
+        <v>-0.3002</v>
       </c>
       <c r="P12" t="n">
         <v>-3.4793</v>
@@ -1390,13 +1390,13 @@
         <v>15.0771</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8512</v>
+        <v>3.598</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3003</v>
+        <v>2.0472</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5506</v>
+        <v>1.5509</v>
       </c>
       <c r="V12" t="n">
         <v>1.6083</v>
@@ -1405,7 +1405,7 @@
         <v>3.642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.033700000000001</v>
+        <v>-2.0337</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3213</v>
+        <v>8.057499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2917</v>
+        <v>4.4097</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0296</v>
+        <v>3.6479</v>
       </c>
       <c r="G13" t="n">
         <v>6.5399</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5407999999999999</v>
+        <v>0.1955</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3563</v>
+        <v>0.2621</v>
       </c>
       <c r="V13" t="n">
         <v>0.3943</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6708</v>
+        <v>4.7489</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3724</v>
+        <v>1.8443</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2984</v>
+        <v>2.9046</v>
       </c>
       <c r="G14" t="n">
         <v>4.458</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2511</v>
+        <v>-0.1731</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4296</v>
+        <v>0.1766</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.401</v>
+        <v>3.5497</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4249</v>
+        <v>-0.338</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9761</v>
+        <v>3.8877</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2396</v>
+        <v>3.4756</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6506</v>
+        <v>1.4814</v>
       </c>
       <c r="I15" t="n">
-        <v>0.589</v>
+        <v>1.9943</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5934</v>
+        <v>1.5314</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8942</v>
+        <v>1.2639</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6993</v>
+        <v>0.2676</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3538</v>
+        <v>1.9442</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2435</v>
+        <v>0.2175</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1103</v>
+        <v>1.7267</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7001</v>
+        <v>0.1463</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6201</v>
+        <v>-0.2278</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08</v>
+        <v>0.3741</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7886</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2738</v>
+        <v>3.0512</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.22</v>
+        <v>0.0482</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4939</v>
+        <v>3.0029</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4756</v>
+        <v>2.9087</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4814</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9943</v>
+        <v>3.4163</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5314</v>
+        <v>1.4869</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2639</v>
+        <v>0.2724</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2676</v>
+        <v>1.2146</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9442</v>
+        <v>1.4218</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2175</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7267</v>
+        <v>2.2018</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1296</v>
+        <v>0.0549</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>-0.279</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0198</v>
+        <v>0.3339</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.455</v>
+        <v>2.328</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1877</v>
+        <v>1.1275</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6427</v>
+        <v>1.2006</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9087</v>
+        <v>1.2396</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.6506</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4163</v>
+        <v>0.589</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4869</v>
+        <v>1.5934</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2724</v>
+        <v>0.8942</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2146</v>
+        <v>0.6993</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4218</v>
+        <v>-0.3538</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>-0.2435</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2018</v>
+        <v>-0.1103</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5412</v>
+        <v>0.6271</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>0.3227</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0263</v>
+        <v>0.3044</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8993</v>
+        <v>2.2632</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0742</v>
+        <v>-0.4281</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9735</v>
+        <v>2.6913</v>
       </c>
       <c r="G18" t="n">
         <v>0.4391</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1634</v>
+        <v>0.2005</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2047</v>
+        <v>-0.1491</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3681</v>
+        <v>0.3497</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.217</v>
+        <v>1.5873</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.015</v>
+        <v>-0.7791</v>
       </c>
       <c r="F19" t="n">
-        <v>2.232</v>
+        <v>2.3664</v>
       </c>
       <c r="G19" t="n">
         <v>1.8203</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2838</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1485</v>
+        <v>0.2829</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0473</v>
+        <v>-1.2867</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9921</v>
+        <v>-4.1776</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9448</v>
+        <v>2.8909</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4153</v>
+        <v>0.1081</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3878</v>
+        <v>0.9614</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8031</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3897</v>
+        <v>-1.1535</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1462</v>
+        <v>0.9011</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5359</v>
+        <v>-2.0547</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0256</v>
+        <v>1.2616</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7584</v>
+        <v>0.0602</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7328</v>
+        <v>1.2014</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4722</v>
+        <v>-0.467</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.617</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1893</v>
+        <v>0.15</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.146</v>
+        <v>-1.3224</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5315</v>
+        <v>-2.6382</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3855</v>
+        <v>1.3158</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1081</v>
+        <v>-0.4153</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9614</v>
+        <v>0.3878</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.8031</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1535</v>
+        <v>-0.3897</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9011</v>
+        <v>1.1462</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0547</v>
+        <v>-1.5359</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2616</v>
+        <v>-0.0256</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0602</v>
+        <v>-0.7584</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2014</v>
+        <v>0.7328</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3262</v>
+        <v>0.2526</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>0.0709</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3554</v>
+        <v>0.1817</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>18.7506</v>
+        <v>22.6824</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8835</v>
+        <v>-1.8833</v>
       </c>
       <c r="F23" t="n">
-        <v>20.6342</v>
+        <v>24.5658</v>
       </c>
       <c r="G23" t="n">
         <v>19.7308</v>
@@ -2227,7 +2227,7 @@
         <v>12.4105</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3001999999999998</v>
+        <v>0.3001999999999996</v>
       </c>
       <c r="M23" t="n">
         <v>7.0204</v>
@@ -2239,7 +2239,7 @@
         <v>10.4574</v>
       </c>
       <c r="P23" t="n">
-        <v>3.479300000000001</v>
+        <v>3.479299999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.077</v>
@@ -2248,13 +2248,13 @@
         <v>18.5563</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8509</v>
+        <v>1.0806</v>
       </c>
       <c r="T23" t="n">
         <v>-1.5509</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3002</v>
+        <v>2.6315</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
